--- a/procesos/importarFacturacion/inputs/nominas/NOMINAS.xlsx
+++ b/procesos/importarFacturacion/inputs/nominas/NOMINAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b8fc90e97c08fff/Nodus/Proyectos/Nodus-app/parche-gestoria/procesos/importarFacturacion/inputs/nominas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{F53A57ED-B9B9-4812-8097-6B871483C203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2C0D892-1462-493E-9FAF-E83368E3946A}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{F53A57ED-B9B9-4812-8097-6B871483C203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A25ED920-943E-4D05-974B-DFD27002D73A}"/>
   <bookViews>
-    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{CB38ADB7-9FCA-4332-9CBA-CBAC1493DAA5}"/>
+    <workbookView xWindow="14205" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CB38ADB7-9FCA-4332-9CBA-CBAC1493DAA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -824,7 +824,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -866,10 +866,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4575,6 +4571,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AD04B2F9-D61B-440F-98D2-ED285336DA54}" name="Tabla133" displayName="Tabla133" ref="A6:R8" totalsRowShown="0" headerRowDxfId="18">
   <autoFilter ref="A6:R8" xr:uid="{AD04B2F9-D61B-440F-98D2-ED285336DA54}"/>
@@ -4596,9 +4596,7 @@
     <tableColumn id="12" xr3:uid="{FF61CC92-7C90-4EA3-B41C-DE1A22A2E257}" name="CONCEPTO FACT" dataDxfId="6">
       <calculatedColumnFormula>IFERROR(VLOOKUP(K7, [1]Conceptos!A:B, 2, FALSE), "")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{2DB76720-957C-4DDA-886A-B23BE4D4194F}" name="IMPORTE" dataDxfId="5" dataCellStyle="Moneda">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(L7, [1]Conceptos!B:C, 2, FALSE), "")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="13" xr3:uid="{2DB76720-957C-4DDA-886A-B23BE4D4194F}" name="IMPORTE" dataDxfId="5" dataCellStyle="Moneda"/>
     <tableColumn id="14" xr3:uid="{C86E0C7A-FAC9-4196-B111-CF60A5C8A864}" name="INICIO" dataDxfId="4">
       <calculatedColumnFormula>IFERROR(VLOOKUP(M7, [1]Conceptos!C:D, 2, FALSE), "")</calculatedColumnFormula>
     </tableColumn>
@@ -5063,10 +5061,7 @@
         <f>IFERROR(VLOOKUP(K7, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M7" s="12" t="str">
-        <f>IFERROR(VLOOKUP(L7, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M7" s="12"/>
       <c r="N7" s="13" t="str">
         <f>IFERROR(VLOOKUP(M7, [1]Conceptos!C:D, 2, FALSE), "")</f>
         <v/>
@@ -5101,15 +5096,12 @@
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="19" t="str">
+      <c r="K8" s="9"/>
+      <c r="L8" s="11" t="str">
         <f>IFERROR(VLOOKUP(K8, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M8" s="12" t="str">
-        <f>IFERROR(VLOOKUP(L8, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M8" s="12"/>
       <c r="N8" s="13" t="str">
         <f>IFERROR(VLOOKUP(M8, [1]Conceptos!C:D, 2, FALSE), "")</f>
         <v/>
@@ -5157,9 +5149,7 @@
         <f>IFERROR(VLOOKUP(K9, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M9" s="12">
-        <v>46</v>
-      </c>
+      <c r="M9" s="12"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="str">
         <f>IFERROR(VLOOKUP(N9, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5204,9 +5194,7 @@
         <f>IFERROR(VLOOKUP(K10, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M10" s="12">
-        <v>966</v>
-      </c>
+      <c r="M10" s="12"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="str">
         <f>IFERROR(VLOOKUP(N10, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5251,9 +5239,7 @@
         <f>IFERROR(VLOOKUP(K11, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M11" s="12">
-        <v>345</v>
-      </c>
+      <c r="M11" s="12"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="str">
         <f>IFERROR(VLOOKUP(N11, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5298,9 +5284,7 @@
         <f>IFERROR(VLOOKUP(K12, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M12" s="12">
-        <v>23</v>
-      </c>
+      <c r="M12" s="12"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="str">
         <f>IFERROR(VLOOKUP(N12, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5345,9 +5329,7 @@
         <f>IFERROR(VLOOKUP(K13, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M13" s="12">
-        <v>529</v>
-      </c>
+      <c r="M13" s="12"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="str">
         <f>IFERROR(VLOOKUP(N13, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5392,9 +5374,7 @@
         <f>IFERROR(VLOOKUP(K14, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M14" s="12">
-        <v>92</v>
-      </c>
+      <c r="M14" s="12"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="str">
         <f>IFERROR(VLOOKUP(N14, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5439,9 +5419,7 @@
         <f>IFERROR(VLOOKUP(K15, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M15" s="12">
-        <v>69</v>
-      </c>
+      <c r="M15" s="12"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="str">
         <f>IFERROR(VLOOKUP(N15, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5486,9 +5464,7 @@
         <f>IFERROR(VLOOKUP(K16, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M16" s="12">
-        <v>253</v>
-      </c>
+      <c r="M16" s="12"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="str">
         <f>IFERROR(VLOOKUP(N16, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5533,9 +5509,7 @@
         <f>IFERROR(VLOOKUP(K17, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M17" s="12">
-        <v>368</v>
-      </c>
+      <c r="M17" s="12"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="str">
         <f>IFERROR(VLOOKUP(N17, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5580,9 +5554,7 @@
         <f>IFERROR(VLOOKUP(K18, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M18" s="12">
-        <v>1058</v>
-      </c>
+      <c r="M18" s="12"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="str">
         <f>IFERROR(VLOOKUP(N18, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5627,9 +5599,7 @@
         <f>IFERROR(VLOOKUP(K19, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M19" s="12">
-        <v>69</v>
-      </c>
+      <c r="M19" s="12"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="str">
         <f>IFERROR(VLOOKUP(N19, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5674,9 +5644,7 @@
         <f>IFERROR(VLOOKUP(K20, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M20" s="12">
-        <v>46</v>
-      </c>
+      <c r="M20" s="12"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="str">
         <f>IFERROR(VLOOKUP(N20, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5721,9 +5689,7 @@
         <f>IFERROR(VLOOKUP(K21, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M21" s="12">
-        <v>3404</v>
-      </c>
+      <c r="M21" s="12"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="str">
         <f>IFERROR(VLOOKUP(N21, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5768,9 +5734,7 @@
         <f>IFERROR(VLOOKUP(K22, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M22" s="12">
-        <v>46</v>
-      </c>
+      <c r="M22" s="12"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="str">
         <f>IFERROR(VLOOKUP(N22, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5815,9 +5779,7 @@
         <f>IFERROR(VLOOKUP(K23, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M23" s="12">
-        <v>161</v>
-      </c>
+      <c r="M23" s="12"/>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="str">
         <f>IFERROR(VLOOKUP(N23, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5862,9 +5824,7 @@
         <f>IFERROR(VLOOKUP(K24, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M24" s="12">
-        <v>69</v>
-      </c>
+      <c r="M24" s="12"/>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="str">
         <f>IFERROR(VLOOKUP(N24, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5909,9 +5869,7 @@
         <f>IFERROR(VLOOKUP(K25, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M25" s="12">
-        <v>184</v>
-      </c>
+      <c r="M25" s="12"/>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="str">
         <f>IFERROR(VLOOKUP(N25, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -5956,9 +5914,7 @@
         <f>IFERROR(VLOOKUP(K26, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M26" s="12">
-        <v>138</v>
-      </c>
+      <c r="M26" s="12"/>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="str">
         <f>IFERROR(VLOOKUP(N26, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6003,9 +5959,7 @@
         <f>IFERROR(VLOOKUP(K27, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M27" s="12">
-        <v>299</v>
-      </c>
+      <c r="M27" s="12"/>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="str">
         <f>IFERROR(VLOOKUP(N27, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6050,9 +6004,7 @@
         <f>IFERROR(VLOOKUP(K28, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M28" s="12">
-        <v>23</v>
-      </c>
+      <c r="M28" s="12"/>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="str">
         <f>IFERROR(VLOOKUP(N28, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6097,9 +6049,7 @@
         <f>IFERROR(VLOOKUP(K29, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M29" s="12">
-        <v>23</v>
-      </c>
+      <c r="M29" s="12"/>
       <c r="N29" s="13"/>
       <c r="O29" s="13" t="str">
         <f>IFERROR(VLOOKUP(N29, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6144,9 +6094,7 @@
         <f>IFERROR(VLOOKUP(K30, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M30" s="12">
-        <v>138</v>
-      </c>
+      <c r="M30" s="12"/>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="str">
         <f>IFERROR(VLOOKUP(N30, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6191,9 +6139,7 @@
         <f>IFERROR(VLOOKUP(K31, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M31" s="12">
-        <v>414</v>
-      </c>
+      <c r="M31" s="12"/>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="str">
         <f>IFERROR(VLOOKUP(N31, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6238,9 +6184,7 @@
         <f>IFERROR(VLOOKUP(K32, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M32" s="12">
-        <v>46</v>
-      </c>
+      <c r="M32" s="12"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="str">
         <f>IFERROR(VLOOKUP(N32, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6285,9 +6229,7 @@
         <f>IFERROR(VLOOKUP(K33, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M33" s="12">
-        <v>276</v>
-      </c>
+      <c r="M33" s="12"/>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="str">
         <f>IFERROR(VLOOKUP(N33, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6332,9 +6274,7 @@
         <f>IFERROR(VLOOKUP(K34, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M34" s="12">
-        <v>92</v>
-      </c>
+      <c r="M34" s="12"/>
       <c r="N34" s="13"/>
       <c r="O34" s="13" t="str">
         <f>IFERROR(VLOOKUP(N34, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6379,9 +6319,7 @@
         <f>IFERROR(VLOOKUP(K35, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M35" s="12">
-        <v>23</v>
-      </c>
+      <c r="M35" s="12"/>
       <c r="N35" s="13"/>
       <c r="O35" s="13" t="str">
         <f>IFERROR(VLOOKUP(N35, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6426,9 +6364,7 @@
         <f>IFERROR(VLOOKUP(K36, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M36" s="12">
-        <v>23</v>
-      </c>
+      <c r="M36" s="12"/>
       <c r="N36" s="13"/>
       <c r="O36" s="13" t="str">
         <f>IFERROR(VLOOKUP(N36, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6473,9 +6409,7 @@
         <f>IFERROR(VLOOKUP(K37, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M37" s="12">
-        <v>115</v>
-      </c>
+      <c r="M37" s="12"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13" t="str">
         <f>IFERROR(VLOOKUP(N37, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6520,9 +6454,7 @@
         <f>IFERROR(VLOOKUP(K38, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M38" s="12">
-        <v>138</v>
-      </c>
+      <c r="M38" s="12"/>
       <c r="N38" s="13"/>
       <c r="O38" s="13" t="str">
         <f>IFERROR(VLOOKUP(N38, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6567,9 +6499,7 @@
         <f>IFERROR(VLOOKUP(K39, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M39" s="12">
-        <v>299</v>
-      </c>
+      <c r="M39" s="12"/>
       <c r="N39" s="13"/>
       <c r="O39" s="13" t="str">
         <f>IFERROR(VLOOKUP(N39, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6614,9 +6544,7 @@
         <f>IFERROR(VLOOKUP(K40, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M40" s="12">
-        <v>23</v>
-      </c>
+      <c r="M40" s="12"/>
       <c r="N40" s="13"/>
       <c r="O40" s="13" t="str">
         <f>IFERROR(VLOOKUP(N40, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6661,9 +6589,7 @@
         <f>IFERROR(VLOOKUP(K41, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M41" s="12">
-        <v>138</v>
-      </c>
+      <c r="M41" s="12"/>
       <c r="N41" s="13"/>
       <c r="O41" s="13" t="str">
         <f>IFERROR(VLOOKUP(N41, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6708,9 +6634,7 @@
         <f>IFERROR(VLOOKUP(K42, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M42" s="12">
-        <v>23</v>
-      </c>
+      <c r="M42" s="12"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13" t="str">
         <f>IFERROR(VLOOKUP(N42, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6755,9 +6679,7 @@
         <f>IFERROR(VLOOKUP(K43, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M43" s="12">
-        <v>46</v>
-      </c>
+      <c r="M43" s="12"/>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="str">
         <f>IFERROR(VLOOKUP(N43, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6802,9 +6724,7 @@
         <f>IFERROR(VLOOKUP(K44, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M44" s="12">
-        <v>92</v>
-      </c>
+      <c r="M44" s="12"/>
       <c r="N44" s="13"/>
       <c r="O44" s="13" t="str">
         <f>IFERROR(VLOOKUP(N44, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6849,9 +6769,7 @@
         <f>IFERROR(VLOOKUP(K45, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M45" s="12">
-        <v>46</v>
-      </c>
+      <c r="M45" s="12"/>
       <c r="N45" s="13"/>
       <c r="O45" s="13" t="str">
         <f>IFERROR(VLOOKUP(N45, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6896,9 +6814,7 @@
         <f>IFERROR(VLOOKUP(K46, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M46" s="12">
-        <v>23</v>
-      </c>
+      <c r="M46" s="12"/>
       <c r="N46" s="13"/>
       <c r="O46" s="13" t="str">
         <f>IFERROR(VLOOKUP(N46, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6943,9 +6859,7 @@
         <f>IFERROR(VLOOKUP(K47, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M47" s="12">
-        <v>115</v>
-      </c>
+      <c r="M47" s="12"/>
       <c r="N47" s="13"/>
       <c r="O47" s="13" t="str">
         <f>IFERROR(VLOOKUP(N47, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -6990,9 +6904,7 @@
         <f>IFERROR(VLOOKUP(K48, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M48" s="12">
-        <v>23</v>
-      </c>
+      <c r="M48" s="12"/>
       <c r="N48" s="13"/>
       <c r="O48" s="13" t="str">
         <f>IFERROR(VLOOKUP(N48, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7037,9 +6949,7 @@
         <f>IFERROR(VLOOKUP(K49, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M49" s="12">
-        <v>230</v>
-      </c>
+      <c r="M49" s="12"/>
       <c r="N49" s="13"/>
       <c r="O49" s="13" t="str">
         <f>IFERROR(VLOOKUP(N49, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7084,9 +6994,7 @@
         <f>IFERROR(VLOOKUP(K50, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M50" s="12">
-        <v>115</v>
-      </c>
+      <c r="M50" s="12"/>
       <c r="N50" s="13"/>
       <c r="O50" s="13" t="str">
         <f>IFERROR(VLOOKUP(N50, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7131,9 +7039,7 @@
         <f>IFERROR(VLOOKUP(K51, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M51" s="12">
-        <v>299</v>
-      </c>
+      <c r="M51" s="12"/>
       <c r="N51" s="13"/>
       <c r="O51" s="13" t="str">
         <f>IFERROR(VLOOKUP(N51, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7178,9 +7084,7 @@
         <f>IFERROR(VLOOKUP(K52, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M52" s="12">
-        <v>184</v>
-      </c>
+      <c r="M52" s="12"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13" t="str">
         <f>IFERROR(VLOOKUP(N52, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7225,9 +7129,7 @@
         <f>IFERROR(VLOOKUP(K53, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M53" s="12">
-        <v>391</v>
-      </c>
+      <c r="M53" s="12"/>
       <c r="N53" s="13"/>
       <c r="O53" s="13" t="str">
         <f>IFERROR(VLOOKUP(N53, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7272,9 +7174,7 @@
         <f>IFERROR(VLOOKUP(K54, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M54" s="12">
-        <v>368</v>
-      </c>
+      <c r="M54" s="12"/>
       <c r="N54" s="13"/>
       <c r="O54" s="13" t="str">
         <f>IFERROR(VLOOKUP(N54, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7319,9 +7219,7 @@
         <f>IFERROR(VLOOKUP(K55, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M55" s="12">
-        <v>46</v>
-      </c>
+      <c r="M55" s="12"/>
       <c r="N55" s="13"/>
       <c r="O55" s="13" t="str">
         <f>IFERROR(VLOOKUP(N55, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7366,9 +7264,7 @@
         <f>IFERROR(VLOOKUP(K56, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M56" s="12">
-        <v>46</v>
-      </c>
+      <c r="M56" s="12"/>
       <c r="N56" s="13"/>
       <c r="O56" s="13" t="str">
         <f>IFERROR(VLOOKUP(N56, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7413,9 +7309,7 @@
         <f>IFERROR(VLOOKUP(K57, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M57" s="12">
-        <v>161</v>
-      </c>
+      <c r="M57" s="12"/>
       <c r="N57" s="13"/>
       <c r="O57" s="13" t="str">
         <f>IFERROR(VLOOKUP(N57, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7460,9 +7354,7 @@
         <f>IFERROR(VLOOKUP(K58, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M58" s="12">
-        <v>138</v>
-      </c>
+      <c r="M58" s="12"/>
       <c r="N58" s="13"/>
       <c r="O58" s="13" t="str">
         <f>IFERROR(VLOOKUP(N58, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7507,9 +7399,7 @@
         <f>IFERROR(VLOOKUP(K59, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M59" s="12">
-        <v>299</v>
-      </c>
+      <c r="M59" s="12"/>
       <c r="N59" s="13"/>
       <c r="O59" s="13" t="str">
         <f>IFERROR(VLOOKUP(N59, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7554,9 +7444,7 @@
         <f>IFERROR(VLOOKUP(K60, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M60" s="12">
-        <v>1564</v>
-      </c>
+      <c r="M60" s="12"/>
       <c r="N60" s="13"/>
       <c r="O60" s="13" t="str">
         <f>IFERROR(VLOOKUP(N60, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7601,9 +7489,7 @@
         <f>IFERROR(VLOOKUP(K61, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M61" s="12">
-        <v>115</v>
-      </c>
+      <c r="M61" s="12"/>
       <c r="N61" s="13"/>
       <c r="O61" s="13" t="str">
         <f>IFERROR(VLOOKUP(N61, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7648,9 +7534,7 @@
         <f>IFERROR(VLOOKUP(K62, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M62" s="12">
-        <v>69</v>
-      </c>
+      <c r="M62" s="12"/>
       <c r="N62" s="13"/>
       <c r="O62" s="13" t="str">
         <f>IFERROR(VLOOKUP(N62, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7695,9 +7579,7 @@
         <f>IFERROR(VLOOKUP(K63, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M63" s="12">
-        <v>851</v>
-      </c>
+      <c r="M63" s="12"/>
       <c r="N63" s="13"/>
       <c r="O63" s="13" t="str">
         <f>IFERROR(VLOOKUP(N63, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7742,9 +7624,7 @@
         <f>IFERROR(VLOOKUP(K64, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M64" s="12">
-        <v>46</v>
-      </c>
+      <c r="M64" s="12"/>
       <c r="N64" s="13"/>
       <c r="O64" s="13" t="str">
         <f>IFERROR(VLOOKUP(N64, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7789,9 +7669,7 @@
         <f>IFERROR(VLOOKUP(K65, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M65" s="12">
-        <v>23</v>
-      </c>
+      <c r="M65" s="12"/>
       <c r="N65" s="13"/>
       <c r="O65" s="13" t="str">
         <f>IFERROR(VLOOKUP(N65, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7836,9 +7714,7 @@
         <f>IFERROR(VLOOKUP(K66, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M66" s="12">
-        <v>253</v>
-      </c>
+      <c r="M66" s="12"/>
       <c r="N66" s="13"/>
       <c r="O66" s="13" t="str">
         <f>IFERROR(VLOOKUP(N66, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7883,9 +7759,7 @@
         <f>IFERROR(VLOOKUP(K67, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M67" s="12">
-        <v>138</v>
-      </c>
+      <c r="M67" s="12"/>
       <c r="N67" s="13"/>
       <c r="O67" s="13" t="str">
         <f>IFERROR(VLOOKUP(N67, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7930,9 +7804,7 @@
         <f>IFERROR(VLOOKUP(K68, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M68" s="12">
-        <v>46</v>
-      </c>
+      <c r="M68" s="12"/>
       <c r="N68" s="13"/>
       <c r="O68" s="13" t="str">
         <f>IFERROR(VLOOKUP(N68, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -7977,9 +7849,7 @@
         <f>IFERROR(VLOOKUP(K69, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M69" s="12">
-        <v>46</v>
-      </c>
+      <c r="M69" s="12"/>
       <c r="N69" s="13"/>
       <c r="O69" s="13" t="str">
         <f>IFERROR(VLOOKUP(N69, [1]Conceptos!D:E, 2, FALSE), "")</f>
@@ -8024,9 +7894,7 @@
         <f>IFERROR(VLOOKUP(K70, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M70" s="12">
-        <v>115</v>
-      </c>
+      <c r="M70" s="12"/>
       <c r="N70" s="13"/>
       <c r="O70" s="13"/>
       <c r="P70" s="13"/>
@@ -8059,9 +7927,7 @@
         <f>IFERROR(VLOOKUP(K71, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M71" s="12">
-        <v>184</v>
-      </c>
+      <c r="M71" s="12"/>
       <c r="N71" s="13"/>
       <c r="O71" s="13"/>
       <c r="P71" s="13"/>
@@ -8094,9 +7960,7 @@
         <f>IFERROR(VLOOKUP(K72, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M72" s="12">
-        <v>345</v>
-      </c>
+      <c r="M72" s="12"/>
       <c r="N72" s="13"/>
       <c r="O72" s="13"/>
       <c r="P72" s="13"/>
@@ -8129,9 +7993,7 @@
         <f>IFERROR(VLOOKUP(K73, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M73" s="12">
-        <v>92</v>
-      </c>
+      <c r="M73" s="12"/>
       <c r="N73" s="13"/>
       <c r="O73" s="13"/>
       <c r="P73" s="13"/>
@@ -8164,9 +8026,7 @@
         <f>IFERROR(VLOOKUP(K74, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M74" s="12">
-        <v>736</v>
-      </c>
+      <c r="M74" s="12"/>
       <c r="N74" s="13"/>
       <c r="O74" s="13"/>
       <c r="P74" s="13"/>
@@ -8199,9 +8059,7 @@
         <f>IFERROR(VLOOKUP(K75, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M75" s="12">
-        <v>276</v>
-      </c>
+      <c r="M75" s="12"/>
       <c r="N75" s="13"/>
       <c r="O75" s="13"/>
       <c r="P75" s="13"/>
@@ -8234,9 +8092,7 @@
         <f>IFERROR(VLOOKUP(K76, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M76" s="12">
-        <v>92</v>
-      </c>
+      <c r="M76" s="12"/>
       <c r="N76" s="13"/>
       <c r="O76" s="13"/>
       <c r="P76" s="13"/>
@@ -8269,9 +8125,7 @@
         <f>IFERROR(VLOOKUP(K77, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M77" s="12">
-        <v>230</v>
-      </c>
+      <c r="M77" s="12"/>
       <c r="N77" s="13"/>
       <c r="O77" s="13"/>
       <c r="P77" s="13"/>
@@ -8304,9 +8158,7 @@
         <f>IFERROR(VLOOKUP(K78, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M78" s="12">
-        <v>621</v>
-      </c>
+      <c r="M78" s="12"/>
       <c r="N78" s="13"/>
       <c r="O78" s="13"/>
       <c r="P78" s="13"/>
@@ -8339,9 +8191,7 @@
         <f>IFERROR(VLOOKUP(K79, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M79" s="12">
-        <v>1104</v>
-      </c>
+      <c r="M79" s="12"/>
       <c r="N79" s="13"/>
       <c r="O79" s="13"/>
       <c r="P79" s="13"/>
@@ -8374,9 +8224,7 @@
         <f>IFERROR(VLOOKUP(K80, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M80" s="12">
-        <v>667</v>
-      </c>
+      <c r="M80" s="12"/>
       <c r="N80" s="13"/>
       <c r="O80" s="13"/>
       <c r="P80" s="13"/>
@@ -8409,9 +8257,7 @@
         <f>IFERROR(VLOOKUP(K81, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M81" s="12">
-        <v>414</v>
-      </c>
+      <c r="M81" s="12"/>
       <c r="N81" s="13"/>
       <c r="O81" s="13"/>
       <c r="P81" s="13"/>
@@ -8444,9 +8290,7 @@
         <f>IFERROR(VLOOKUP(K82, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M82" s="12">
-        <v>253</v>
-      </c>
+      <c r="M82" s="12"/>
       <c r="N82" s="13"/>
       <c r="O82" s="13"/>
       <c r="P82" s="13"/>
@@ -8479,9 +8323,7 @@
         <f>IFERROR(VLOOKUP(K83, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M83" s="12">
-        <v>2369</v>
-      </c>
+      <c r="M83" s="12"/>
       <c r="N83" s="13"/>
       <c r="O83" s="13"/>
       <c r="P83" s="13"/>
@@ -8514,9 +8356,7 @@
         <f>IFERROR(VLOOKUP(K84, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M84" s="12">
-        <v>782</v>
-      </c>
+      <c r="M84" s="12"/>
       <c r="N84" s="13"/>
       <c r="O84" s="13"/>
       <c r="P84" s="13"/>
@@ -8549,9 +8389,7 @@
         <f>IFERROR(VLOOKUP(K85, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M85" s="12">
-        <v>253</v>
-      </c>
+      <c r="M85" s="12"/>
       <c r="N85" s="13"/>
       <c r="O85" s="13"/>
       <c r="P85" s="13"/>
@@ -8584,9 +8422,7 @@
         <f>IFERROR(VLOOKUP(K86, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M86" s="12">
-        <v>23</v>
-      </c>
+      <c r="M86" s="12"/>
       <c r="N86" s="13"/>
       <c r="O86" s="13"/>
       <c r="P86" s="13"/>
@@ -8619,9 +8455,7 @@
         <f>IFERROR(VLOOKUP(K87, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M87" s="12">
-        <v>23</v>
-      </c>
+      <c r="M87" s="12"/>
       <c r="N87" s="13"/>
       <c r="O87" s="13"/>
       <c r="P87" s="13"/>
@@ -8654,9 +8488,7 @@
         <f>IFERROR(VLOOKUP(K88, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M88" s="12">
-        <v>23</v>
-      </c>
+      <c r="M88" s="12"/>
       <c r="N88" s="13"/>
       <c r="O88" s="13"/>
       <c r="P88" s="13"/>
@@ -8689,9 +8521,7 @@
         <f>IFERROR(VLOOKUP(K89, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M89" s="12">
-        <v>115</v>
-      </c>
+      <c r="M89" s="12"/>
       <c r="N89" s="13"/>
       <c r="O89" s="13"/>
       <c r="P89" s="13"/>
@@ -8724,9 +8554,7 @@
         <f>IFERROR(VLOOKUP(K90, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M90" s="12">
-        <v>92</v>
-      </c>
+      <c r="M90" s="12"/>
       <c r="N90" s="13"/>
       <c r="O90" s="13"/>
       <c r="P90" s="13"/>
@@ -8759,9 +8587,7 @@
         <f>IFERROR(VLOOKUP(K91, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M91" s="12">
-        <v>161</v>
-      </c>
+      <c r="M91" s="12"/>
       <c r="N91" s="13"/>
       <c r="O91" s="13"/>
       <c r="P91" s="13"/>
@@ -8794,9 +8620,7 @@
         <f>IFERROR(VLOOKUP(K92, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M92" s="12">
-        <v>391</v>
-      </c>
+      <c r="M92" s="12"/>
       <c r="N92" s="13"/>
       <c r="O92" s="13"/>
       <c r="P92" s="13"/>
@@ -8829,9 +8653,7 @@
         <f>IFERROR(VLOOKUP(K93, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M93" s="12">
-        <v>253</v>
-      </c>
+      <c r="M93" s="12"/>
       <c r="N93" s="13"/>
       <c r="O93" s="13"/>
       <c r="P93" s="13"/>
@@ -8864,9 +8686,7 @@
         <f>IFERROR(VLOOKUP(K94, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M94" s="12">
-        <v>23</v>
-      </c>
+      <c r="M94" s="12"/>
       <c r="N94" s="13"/>
       <c r="O94" s="13"/>
       <c r="P94" s="13"/>
@@ -8899,9 +8719,7 @@
         <f>IFERROR(VLOOKUP(K95, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M95" s="12">
-        <v>874</v>
-      </c>
+      <c r="M95" s="12"/>
       <c r="N95" s="13"/>
       <c r="O95" s="13"/>
       <c r="P95" s="13"/>
@@ -8934,9 +8752,7 @@
         <f>IFERROR(VLOOKUP(K96, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M96" s="12">
-        <v>207</v>
-      </c>
+      <c r="M96" s="12"/>
       <c r="N96" s="13"/>
       <c r="O96" s="13"/>
       <c r="P96" s="13"/>
@@ -8969,9 +8785,7 @@
         <f>IFERROR(VLOOKUP(K97, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M97" s="12">
-        <v>23</v>
-      </c>
+      <c r="M97" s="12"/>
       <c r="N97" s="13"/>
       <c r="O97" s="13"/>
       <c r="P97" s="13"/>
@@ -9004,9 +8818,7 @@
         <f>IFERROR(VLOOKUP(K98, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M98" s="12">
-        <v>598</v>
-      </c>
+      <c r="M98" s="12"/>
       <c r="N98" s="13"/>
       <c r="O98" s="13"/>
       <c r="P98" s="13"/>
@@ -9039,9 +8851,7 @@
         <f>IFERROR(VLOOKUP(K99, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M99" s="12">
-        <v>46</v>
-      </c>
+      <c r="M99" s="12"/>
       <c r="N99" s="13"/>
       <c r="O99" s="13"/>
       <c r="P99" s="13"/>
@@ -9074,9 +8884,7 @@
         <f>IFERROR(VLOOKUP(K100, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M100" s="12">
-        <v>161</v>
-      </c>
+      <c r="M100" s="12"/>
       <c r="N100" s="13"/>
       <c r="O100" s="13"/>
       <c r="P100" s="13"/>
@@ -9109,9 +8917,7 @@
         <f>IFERROR(VLOOKUP(K101, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M101" s="12">
-        <v>46</v>
-      </c>
+      <c r="M101" s="12"/>
       <c r="N101" s="13"/>
       <c r="O101" s="13"/>
       <c r="P101" s="13"/>
@@ -9144,9 +8950,7 @@
         <f>IFERROR(VLOOKUP(K102, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M102" s="12">
-        <v>207</v>
-      </c>
+      <c r="M102" s="12"/>
       <c r="N102" s="13"/>
       <c r="O102" s="13"/>
       <c r="P102" s="13"/>
@@ -9179,9 +8983,7 @@
         <f>IFERROR(VLOOKUP(K103, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M103" s="12">
-        <v>322</v>
-      </c>
+      <c r="M103" s="12"/>
       <c r="N103" s="13"/>
       <c r="O103" s="13"/>
       <c r="P103" s="13"/>
@@ -9214,9 +9016,7 @@
         <f>IFERROR(VLOOKUP(K104, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M104" s="12">
-        <v>391</v>
-      </c>
+      <c r="M104" s="12"/>
       <c r="N104" s="13"/>
       <c r="O104" s="13"/>
       <c r="P104" s="13"/>
@@ -9249,9 +9049,7 @@
         <f>IFERROR(VLOOKUP(K105, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M105" s="12">
-        <v>92</v>
-      </c>
+      <c r="M105" s="12"/>
       <c r="N105" s="13"/>
       <c r="O105" s="13"/>
       <c r="P105" s="13"/>
@@ -9284,9 +9082,7 @@
         <f>IFERROR(VLOOKUP(K106, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M106" s="12">
-        <v>115</v>
-      </c>
+      <c r="M106" s="12"/>
       <c r="N106" s="13"/>
       <c r="O106" s="13"/>
       <c r="P106" s="13"/>
@@ -9319,9 +9115,7 @@
         <f>IFERROR(VLOOKUP(K107, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M107" s="12">
-        <v>138</v>
-      </c>
+      <c r="M107" s="12"/>
       <c r="N107" s="13"/>
       <c r="O107" s="13"/>
       <c r="P107" s="13"/>
@@ -9354,9 +9148,7 @@
         <f>IFERROR(VLOOKUP(K108, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M108" s="12">
-        <v>69</v>
-      </c>
+      <c r="M108" s="12"/>
       <c r="N108" s="13"/>
       <c r="O108" s="13"/>
       <c r="P108" s="13"/>
@@ -9389,9 +9181,7 @@
         <f>IFERROR(VLOOKUP(K109, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M109" s="12">
-        <v>46</v>
-      </c>
+      <c r="M109" s="12"/>
       <c r="N109" s="13"/>
       <c r="O109" s="13"/>
       <c r="P109" s="13"/>
@@ -9424,9 +9214,7 @@
         <f>IFERROR(VLOOKUP(K110, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M110" s="12">
-        <v>782</v>
-      </c>
+      <c r="M110" s="12"/>
       <c r="N110" s="13"/>
       <c r="O110" s="13"/>
       <c r="P110" s="13"/>
@@ -9459,9 +9247,7 @@
         <f>IFERROR(VLOOKUP(K111, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M111" s="12">
-        <v>230</v>
-      </c>
+      <c r="M111" s="12"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
       <c r="P111" s="13"/>
@@ -9494,9 +9280,7 @@
         <f>IFERROR(VLOOKUP(K112, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M112" s="12">
-        <v>23</v>
-      </c>
+      <c r="M112" s="12"/>
       <c r="N112" s="13"/>
       <c r="O112" s="13"/>
       <c r="P112" s="13"/>
@@ -9529,9 +9313,7 @@
         <f>IFERROR(VLOOKUP(K113, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M113" s="12">
-        <v>161</v>
-      </c>
+      <c r="M113" s="12"/>
       <c r="N113" s="13"/>
       <c r="O113" s="13"/>
       <c r="P113" s="13"/>
@@ -9564,9 +9346,7 @@
         <f>IFERROR(VLOOKUP(K114, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M114" s="12">
-        <v>69</v>
-      </c>
+      <c r="M114" s="12"/>
       <c r="N114" s="13"/>
       <c r="O114" s="13"/>
       <c r="P114" s="13"/>
@@ -9599,9 +9379,7 @@
         <f>IFERROR(VLOOKUP(K115, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M115" s="12">
-        <v>736</v>
-      </c>
+      <c r="M115" s="12"/>
       <c r="N115" s="13"/>
       <c r="O115" s="13"/>
       <c r="P115" s="13"/>
@@ -9634,9 +9412,7 @@
         <f>IFERROR(VLOOKUP(K116, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M116" s="12">
-        <v>552</v>
-      </c>
+      <c r="M116" s="12"/>
       <c r="N116" s="13"/>
       <c r="O116" s="13"/>
       <c r="P116" s="13"/>
@@ -9669,9 +9445,7 @@
         <f>IFERROR(VLOOKUP(K117, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M117" s="12">
-        <v>69</v>
-      </c>
+      <c r="M117" s="12"/>
       <c r="N117" s="13"/>
       <c r="O117" s="13"/>
       <c r="P117" s="13"/>
@@ -9704,9 +9478,7 @@
         <f>IFERROR(VLOOKUP(K118, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M118" s="12">
-        <v>115</v>
-      </c>
+      <c r="M118" s="12"/>
       <c r="N118" s="13"/>
       <c r="O118" s="13"/>
       <c r="P118" s="13"/>
@@ -9739,9 +9511,7 @@
         <f>IFERROR(VLOOKUP(K119, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M119" s="12">
-        <v>69</v>
-      </c>
+      <c r="M119" s="12"/>
       <c r="N119" s="13"/>
       <c r="O119" s="13"/>
       <c r="P119" s="13"/>
@@ -9774,9 +9544,7 @@
         <f>IFERROR(VLOOKUP(K120, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M120" s="12">
-        <v>184</v>
-      </c>
+      <c r="M120" s="12"/>
       <c r="N120" s="13"/>
       <c r="O120" s="13"/>
       <c r="P120" s="13"/>
@@ -9809,9 +9577,7 @@
         <f>IFERROR(VLOOKUP(K121, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M121" s="12">
-        <v>23</v>
-      </c>
+      <c r="M121" s="12"/>
       <c r="N121" s="13"/>
       <c r="O121" s="13"/>
       <c r="P121" s="13"/>
@@ -9844,9 +9610,7 @@
         <f>IFERROR(VLOOKUP(K122, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M122" s="12">
-        <v>207</v>
-      </c>
+      <c r="M122" s="12"/>
       <c r="N122" s="13"/>
       <c r="O122" s="13"/>
       <c r="P122" s="13"/>
@@ -9879,9 +9643,7 @@
         <f>IFERROR(VLOOKUP(K123, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M123" s="12">
-        <v>23</v>
-      </c>
+      <c r="M123" s="12"/>
       <c r="N123" s="13"/>
       <c r="O123" s="13"/>
       <c r="P123" s="13"/>
@@ -9914,9 +9676,7 @@
         <f>IFERROR(VLOOKUP(K124, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M124" s="12">
-        <v>92</v>
-      </c>
+      <c r="M124" s="12"/>
       <c r="N124" s="13"/>
       <c r="O124" s="13"/>
       <c r="P124" s="13"/>
@@ -9949,9 +9709,7 @@
         <f>IFERROR(VLOOKUP(K125, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M125" s="12">
-        <v>782</v>
-      </c>
+      <c r="M125" s="12"/>
       <c r="N125" s="13"/>
       <c r="O125" s="13"/>
       <c r="P125" s="13"/>
@@ -9984,9 +9742,7 @@
         <f>IFERROR(VLOOKUP(K126, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M126" s="12">
-        <v>46</v>
-      </c>
+      <c r="M126" s="12"/>
       <c r="N126" s="13"/>
       <c r="O126" s="13"/>
       <c r="P126" s="13"/>
@@ -10019,9 +9775,7 @@
         <f>IFERROR(VLOOKUP(K127, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M127" s="12">
-        <v>115</v>
-      </c>
+      <c r="M127" s="12"/>
       <c r="N127" s="13"/>
       <c r="O127" s="13"/>
       <c r="P127" s="13"/>
@@ -10054,9 +9808,7 @@
         <f>IFERROR(VLOOKUP(K128, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M128" s="12">
-        <v>138</v>
-      </c>
+      <c r="M128" s="12"/>
       <c r="N128" s="13"/>
       <c r="O128" s="13"/>
       <c r="P128" s="13"/>
@@ -10089,9 +9841,7 @@
         <f>IFERROR(VLOOKUP(K129, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M129" s="12">
-        <v>23</v>
-      </c>
+      <c r="M129" s="12"/>
       <c r="N129" s="13"/>
       <c r="O129" s="13"/>
       <c r="P129" s="13"/>
@@ -10124,9 +9874,7 @@
         <f>IFERROR(VLOOKUP(K130, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M130" s="12">
-        <v>230</v>
-      </c>
+      <c r="M130" s="12"/>
       <c r="N130" s="13"/>
       <c r="O130" s="13"/>
       <c r="P130" s="13"/>
@@ -10159,9 +9907,7 @@
         <f>IFERROR(VLOOKUP(K131, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M131" s="12">
-        <v>161</v>
-      </c>
+      <c r="M131" s="12"/>
       <c r="N131" s="13"/>
       <c r="O131" s="13"/>
       <c r="P131" s="13"/>
@@ -10194,9 +9940,7 @@
         <f>IFERROR(VLOOKUP(K132, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M132" s="12">
-        <v>184</v>
-      </c>
+      <c r="M132" s="12"/>
       <c r="N132" s="13"/>
       <c r="O132" s="13"/>
       <c r="P132" s="13"/>
@@ -10229,9 +9973,7 @@
         <f>IFERROR(VLOOKUP(K133, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M133" s="12">
-        <v>69</v>
-      </c>
+      <c r="M133" s="12"/>
       <c r="N133" s="13"/>
       <c r="O133" s="13"/>
       <c r="P133" s="13"/>
@@ -10264,9 +10006,7 @@
         <f>IFERROR(VLOOKUP(K134, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M134" s="12">
-        <v>115</v>
-      </c>
+      <c r="M134" s="12"/>
       <c r="N134" s="13"/>
       <c r="O134" s="13"/>
       <c r="P134" s="13"/>
@@ -10299,9 +10039,7 @@
         <f>IFERROR(VLOOKUP(K135, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M135" s="12">
-        <v>23</v>
-      </c>
+      <c r="M135" s="12"/>
       <c r="N135" s="13"/>
       <c r="O135" s="13"/>
       <c r="P135" s="13"/>
@@ -10334,9 +10072,7 @@
         <f>IFERROR(VLOOKUP(K136, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M136" s="12">
-        <v>115</v>
-      </c>
+      <c r="M136" s="12"/>
       <c r="N136" s="13"/>
       <c r="O136" s="13"/>
       <c r="P136" s="13"/>
@@ -10369,9 +10105,7 @@
         <f>IFERROR(VLOOKUP(K137, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M137" s="12">
-        <v>92</v>
-      </c>
+      <c r="M137" s="12"/>
       <c r="N137" s="13"/>
       <c r="O137" s="13"/>
       <c r="P137" s="13"/>
@@ -10404,9 +10138,7 @@
         <f>IFERROR(VLOOKUP(K138, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M138" s="12">
-        <v>46</v>
-      </c>
+      <c r="M138" s="12"/>
       <c r="N138" s="13"/>
       <c r="O138" s="13"/>
       <c r="P138" s="13"/>
@@ -10439,9 +10171,7 @@
         <f>IFERROR(VLOOKUP(K139, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M139" s="12">
-        <v>920</v>
-      </c>
+      <c r="M139" s="12"/>
       <c r="N139" s="13"/>
       <c r="O139" s="13"/>
       <c r="P139" s="13"/>
@@ -10474,9 +10204,7 @@
         <f>IFERROR(VLOOKUP(K140, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M140" s="12">
-        <v>2852</v>
-      </c>
+      <c r="M140" s="12"/>
       <c r="N140" s="13"/>
       <c r="O140" s="13"/>
       <c r="P140" s="13"/>
@@ -10509,9 +10237,7 @@
         <f>IFERROR(VLOOKUP(K141, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M141" s="12">
-        <v>46</v>
-      </c>
+      <c r="M141" s="12"/>
       <c r="N141" s="13"/>
       <c r="O141" s="13"/>
       <c r="P141" s="13"/>
@@ -10544,9 +10270,7 @@
         <f>IFERROR(VLOOKUP(K142, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M142" s="12">
-        <v>23</v>
-      </c>
+      <c r="M142" s="12"/>
       <c r="N142" s="13"/>
       <c r="O142" s="13"/>
       <c r="P142" s="13"/>
@@ -10579,9 +10303,7 @@
         <f>IFERROR(VLOOKUP(K143, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M143" s="12">
-        <v>46</v>
-      </c>
+      <c r="M143" s="12"/>
       <c r="N143" s="13"/>
       <c r="O143" s="13"/>
       <c r="P143" s="13"/>
@@ -10614,9 +10336,7 @@
         <f>IFERROR(VLOOKUP(K144, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M144" s="12">
-        <v>23</v>
-      </c>
+      <c r="M144" s="12"/>
       <c r="N144" s="13"/>
       <c r="O144" s="13"/>
       <c r="P144" s="13"/>
@@ -10649,9 +10369,7 @@
         <f>IFERROR(VLOOKUP(K145, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M145" s="12">
-        <v>23</v>
-      </c>
+      <c r="M145" s="12"/>
       <c r="N145" s="13"/>
       <c r="O145" s="13"/>
       <c r="P145" s="13"/>
@@ -10684,9 +10402,7 @@
         <f>IFERROR(VLOOKUP(K146, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M146" s="12">
-        <v>161</v>
-      </c>
+      <c r="M146" s="12"/>
       <c r="N146" s="13"/>
       <c r="O146" s="13"/>
       <c r="P146" s="13"/>
@@ -10719,9 +10435,7 @@
         <f>IFERROR(VLOOKUP(K147, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M147" s="12">
-        <v>414</v>
-      </c>
+      <c r="M147" s="12"/>
       <c r="N147" s="13"/>
       <c r="O147" s="13"/>
       <c r="P147" s="13"/>
@@ -10754,9 +10468,7 @@
         <f>IFERROR(VLOOKUP(K148, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M148" s="12">
-        <v>621</v>
-      </c>
+      <c r="M148" s="12"/>
       <c r="N148" s="13"/>
       <c r="O148" s="13"/>
       <c r="P148" s="13"/>
@@ -10789,9 +10501,7 @@
         <f>IFERROR(VLOOKUP(K149, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M149" s="12">
-        <v>184</v>
-      </c>
+      <c r="M149" s="12"/>
       <c r="N149" s="13"/>
       <c r="O149" s="13"/>
       <c r="P149" s="13"/>
@@ -10824,9 +10534,7 @@
         <f>IFERROR(VLOOKUP(K150, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M150" s="12">
-        <v>460</v>
-      </c>
+      <c r="M150" s="12"/>
       <c r="N150" s="13"/>
       <c r="O150" s="13"/>
       <c r="P150" s="13"/>
@@ -10859,9 +10567,7 @@
         <f>IFERROR(VLOOKUP(K151, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M151" s="12">
-        <v>92</v>
-      </c>
+      <c r="M151" s="12"/>
       <c r="N151" s="13"/>
       <c r="O151" s="13"/>
       <c r="P151" s="13"/>
@@ -10894,9 +10600,7 @@
         <f>IFERROR(VLOOKUP(K152, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M152" s="12">
-        <v>575</v>
-      </c>
+      <c r="M152" s="12"/>
       <c r="N152" s="13"/>
       <c r="O152" s="13"/>
       <c r="P152" s="13"/>
@@ -10929,9 +10633,7 @@
         <f>IFERROR(VLOOKUP(K153, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M153" s="12">
-        <v>230</v>
-      </c>
+      <c r="M153" s="12"/>
       <c r="N153" s="13"/>
       <c r="O153" s="13"/>
       <c r="P153" s="13"/>
@@ -10964,9 +10666,7 @@
         <f>IFERROR(VLOOKUP(K154, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M154" s="12">
-        <v>23</v>
-      </c>
+      <c r="M154" s="12"/>
       <c r="N154" s="13"/>
       <c r="O154" s="13"/>
       <c r="P154" s="13"/>
@@ -10999,9 +10699,7 @@
         <f>IFERROR(VLOOKUP(K155, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M155" s="12">
-        <v>46</v>
-      </c>
+      <c r="M155" s="12"/>
       <c r="N155" s="13"/>
       <c r="O155" s="13"/>
       <c r="P155" s="13"/>
@@ -11034,9 +10732,7 @@
         <f>IFERROR(VLOOKUP(K156, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M156" s="12">
-        <v>345</v>
-      </c>
+      <c r="M156" s="12"/>
       <c r="N156" s="13"/>
       <c r="O156" s="13"/>
       <c r="P156" s="13"/>
@@ -11069,9 +10765,7 @@
         <f>IFERROR(VLOOKUP(K157, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M157" s="12">
-        <v>46</v>
-      </c>
+      <c r="M157" s="12"/>
       <c r="N157" s="13"/>
       <c r="O157" s="13"/>
       <c r="P157" s="13"/>
@@ -11104,9 +10798,7 @@
         <f>IFERROR(VLOOKUP(K158, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M158" s="12">
-        <v>46</v>
-      </c>
+      <c r="M158" s="12"/>
       <c r="N158" s="13"/>
       <c r="O158" s="13"/>
       <c r="P158" s="13"/>
@@ -11139,9 +10831,7 @@
         <f>IFERROR(VLOOKUP(K159, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M159" s="12">
-        <v>115</v>
-      </c>
+      <c r="M159" s="12"/>
       <c r="N159" s="13"/>
       <c r="O159" s="13"/>
       <c r="P159" s="13"/>
@@ -11174,9 +10864,7 @@
         <f>IFERROR(VLOOKUP(K160, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M160" s="12">
-        <v>23</v>
-      </c>
+      <c r="M160" s="12"/>
       <c r="N160" s="13"/>
       <c r="O160" s="13"/>
       <c r="P160" s="13"/>
@@ -11209,9 +10897,7 @@
         <f>IFERROR(VLOOKUP(K161, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M161" s="12">
-        <v>46</v>
-      </c>
+      <c r="M161" s="12"/>
       <c r="N161" s="13"/>
       <c r="O161" s="13"/>
       <c r="P161" s="13"/>
@@ -11244,9 +10930,7 @@
         <f>IFERROR(VLOOKUP(K162, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M162" s="12">
-        <v>69</v>
-      </c>
+      <c r="M162" s="12"/>
       <c r="N162" s="13"/>
       <c r="O162" s="13"/>
       <c r="P162" s="13"/>
@@ -11279,9 +10963,7 @@
         <f>IFERROR(VLOOKUP(K163, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M163" s="12">
-        <v>69</v>
-      </c>
+      <c r="M163" s="12"/>
       <c r="N163" s="13"/>
       <c r="O163" s="13"/>
       <c r="P163" s="13"/>
@@ -11314,9 +10996,7 @@
         <f>IFERROR(VLOOKUP(K164, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M164" s="12">
-        <v>1058</v>
-      </c>
+      <c r="M164" s="12"/>
       <c r="N164" s="13"/>
       <c r="O164" s="13"/>
       <c r="P164" s="13"/>
@@ -11349,9 +11029,7 @@
         <f>IFERROR(VLOOKUP(K165, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M165" s="12">
-        <v>230</v>
-      </c>
+      <c r="M165" s="12"/>
       <c r="N165" s="13"/>
       <c r="O165" s="13"/>
       <c r="P165" s="13"/>
@@ -11384,9 +11062,7 @@
         <f>IFERROR(VLOOKUP(K166, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M166" s="12">
-        <v>138</v>
-      </c>
+      <c r="M166" s="12"/>
       <c r="N166" s="13"/>
       <c r="O166" s="13"/>
       <c r="P166" s="13"/>
@@ -11419,9 +11095,7 @@
         <f>IFERROR(VLOOKUP(K167, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M167" s="12">
-        <v>184</v>
-      </c>
+      <c r="M167" s="12"/>
       <c r="N167" s="13"/>
       <c r="O167" s="13"/>
       <c r="P167" s="13"/>
@@ -11454,9 +11128,7 @@
         <f>IFERROR(VLOOKUP(K168, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M168" s="12">
-        <v>92</v>
-      </c>
+      <c r="M168" s="12"/>
       <c r="N168" s="13"/>
       <c r="O168" s="13"/>
       <c r="P168" s="13"/>
@@ -11489,9 +11161,7 @@
         <f>IFERROR(VLOOKUP(K169, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M169" s="12">
-        <v>69</v>
-      </c>
+      <c r="M169" s="12"/>
       <c r="N169" s="13"/>
       <c r="O169" s="13"/>
       <c r="P169" s="13"/>
@@ -11524,9 +11194,7 @@
         <f>IFERROR(VLOOKUP(K170, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M170" s="12">
-        <v>23</v>
-      </c>
+      <c r="M170" s="12"/>
       <c r="N170" s="13"/>
       <c r="O170" s="13"/>
       <c r="P170" s="13"/>
@@ -11559,9 +11227,7 @@
         <f>IFERROR(VLOOKUP(K171, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M171" s="12">
-        <v>23</v>
-      </c>
+      <c r="M171" s="12"/>
       <c r="N171" s="13"/>
       <c r="O171" s="13"/>
       <c r="P171" s="13"/>
@@ -11594,9 +11260,7 @@
         <f>IFERROR(VLOOKUP(K172, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M172" s="12">
-        <v>69</v>
-      </c>
+      <c r="M172" s="12"/>
       <c r="N172" s="13"/>
       <c r="O172" s="13"/>
       <c r="P172" s="13"/>
@@ -11629,9 +11293,7 @@
         <f>IFERROR(VLOOKUP(K173, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M173" s="12">
-        <v>253</v>
-      </c>
+      <c r="M173" s="12"/>
       <c r="N173" s="13"/>
       <c r="O173" s="13"/>
       <c r="P173" s="13"/>
@@ -11664,9 +11326,7 @@
         <f>IFERROR(VLOOKUP(K174, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M174" s="12">
-        <v>115</v>
-      </c>
+      <c r="M174" s="12"/>
       <c r="N174" s="13"/>
       <c r="O174" s="13"/>
       <c r="P174" s="13"/>
@@ -11699,9 +11359,7 @@
         <f>IFERROR(VLOOKUP(K175, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M175" s="12">
-        <v>138</v>
-      </c>
+      <c r="M175" s="12"/>
       <c r="N175" s="13"/>
       <c r="O175" s="13"/>
       <c r="P175" s="13"/>
@@ -11734,9 +11392,7 @@
         <f>IFERROR(VLOOKUP(K176, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M176" s="12">
-        <v>115</v>
-      </c>
+      <c r="M176" s="12"/>
       <c r="N176" s="13"/>
       <c r="O176" s="13"/>
       <c r="P176" s="13"/>
@@ -11769,9 +11425,7 @@
         <f>IFERROR(VLOOKUP(K177, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M177" s="12">
-        <v>115</v>
-      </c>
+      <c r="M177" s="12"/>
       <c r="N177" s="13"/>
       <c r="O177" s="13"/>
       <c r="P177" s="13"/>
@@ -11804,9 +11458,7 @@
         <f>IFERROR(VLOOKUP(K178, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M178" s="12">
-        <v>69</v>
-      </c>
+      <c r="M178" s="12"/>
       <c r="N178" s="13"/>
       <c r="O178" s="13"/>
       <c r="P178" s="13"/>
@@ -11839,9 +11491,7 @@
         <f>IFERROR(VLOOKUP(K179, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M179" s="12">
-        <v>368</v>
-      </c>
+      <c r="M179" s="12"/>
       <c r="N179" s="13"/>
       <c r="O179" s="13"/>
       <c r="P179" s="13"/>
@@ -11874,9 +11524,7 @@
         <f>IFERROR(VLOOKUP(K180, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M180" s="12">
-        <v>184</v>
-      </c>
+      <c r="M180" s="12"/>
       <c r="N180" s="13"/>
       <c r="O180" s="13"/>
       <c r="P180" s="13"/>
@@ -11909,9 +11557,7 @@
         <f>IFERROR(VLOOKUP(K181, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M181" s="12">
-        <v>115</v>
-      </c>
+      <c r="M181" s="12"/>
       <c r="N181" s="13"/>
       <c r="O181" s="13"/>
       <c r="P181" s="13"/>
@@ -11944,9 +11590,7 @@
         <f>IFERROR(VLOOKUP(K182, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M182" s="12">
-        <v>575</v>
-      </c>
+      <c r="M182" s="12"/>
       <c r="N182" s="13"/>
       <c r="O182" s="13"/>
       <c r="P182" s="13"/>
@@ -11979,9 +11623,7 @@
         <f>IFERROR(VLOOKUP(K183, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M183" s="12">
-        <v>115</v>
-      </c>
+      <c r="M183" s="12"/>
       <c r="N183" s="13"/>
       <c r="O183" s="13"/>
       <c r="P183" s="13"/>
@@ -12014,9 +11656,7 @@
         <f>IFERROR(VLOOKUP(K184, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M184" s="12">
-        <v>460</v>
-      </c>
+      <c r="M184" s="12"/>
       <c r="N184" s="13"/>
       <c r="O184" s="13"/>
       <c r="P184" s="13"/>
@@ -12049,9 +11689,7 @@
         <f>IFERROR(VLOOKUP(K185, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M185" s="12">
-        <v>322</v>
-      </c>
+      <c r="M185" s="12"/>
       <c r="N185" s="13"/>
       <c r="O185" s="13"/>
       <c r="P185" s="13"/>
@@ -12084,9 +11722,7 @@
         <f>IFERROR(VLOOKUP(K186, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M186" s="12">
-        <v>161</v>
-      </c>
+      <c r="M186" s="12"/>
       <c r="N186" s="13"/>
       <c r="O186" s="13"/>
       <c r="P186" s="13"/>
@@ -12119,9 +11755,7 @@
         <f>IFERROR(VLOOKUP(K187, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M187" s="12">
-        <v>69</v>
-      </c>
+      <c r="M187" s="12"/>
       <c r="N187" s="13"/>
       <c r="O187" s="13"/>
       <c r="P187" s="13"/>
@@ -12154,9 +11788,7 @@
         <f>IFERROR(VLOOKUP(K188, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M188" s="12">
-        <v>46</v>
-      </c>
+      <c r="M188" s="12"/>
       <c r="N188" s="13"/>
       <c r="O188" s="13"/>
       <c r="P188" s="13"/>
@@ -12189,9 +11821,7 @@
         <f>IFERROR(VLOOKUP(K189, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M189" s="12">
-        <v>46</v>
-      </c>
+      <c r="M189" s="12"/>
       <c r="N189" s="13"/>
       <c r="O189" s="13"/>
       <c r="P189" s="13"/>
@@ -12224,9 +11854,7 @@
         <f>IFERROR(VLOOKUP(K190, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M190" s="12">
-        <v>115</v>
-      </c>
+      <c r="M190" s="12"/>
       <c r="N190" s="13"/>
       <c r="O190" s="13"/>
       <c r="P190" s="13"/>
@@ -12259,9 +11887,7 @@
         <f>IFERROR(VLOOKUP(K191, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M191" s="12">
-        <v>437</v>
-      </c>
+      <c r="M191" s="12"/>
       <c r="N191" s="13"/>
       <c r="O191" s="13"/>
       <c r="P191" s="13"/>
@@ -12294,9 +11920,7 @@
         <f>IFERROR(VLOOKUP(K192, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M192" s="12">
-        <v>207</v>
-      </c>
+      <c r="M192" s="12"/>
       <c r="N192" s="13"/>
       <c r="O192" s="13"/>
       <c r="P192" s="13"/>
@@ -12329,9 +11953,7 @@
         <f>IFERROR(VLOOKUP(K193, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M193" s="12">
-        <v>207</v>
-      </c>
+      <c r="M193" s="12"/>
       <c r="N193" s="13"/>
       <c r="O193" s="13"/>
       <c r="P193" s="13"/>
@@ -12364,9 +11986,7 @@
         <f>IFERROR(VLOOKUP(K194, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M194" s="12">
-        <v>46</v>
-      </c>
+      <c r="M194" s="12"/>
       <c r="N194" s="13"/>
       <c r="O194" s="13"/>
       <c r="P194" s="13"/>
@@ -12399,9 +12019,7 @@
         <f>IFERROR(VLOOKUP(K195, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M195" s="12">
-        <v>736</v>
-      </c>
+      <c r="M195" s="12"/>
       <c r="N195" s="13"/>
       <c r="O195" s="13"/>
       <c r="P195" s="13"/>
@@ -12434,9 +12052,7 @@
         <f>IFERROR(VLOOKUP(K196, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M196" s="12">
-        <v>46</v>
-      </c>
+      <c r="M196" s="12"/>
       <c r="N196" s="13"/>
       <c r="O196" s="13"/>
       <c r="P196" s="13"/>
@@ -12469,9 +12085,7 @@
         <f>IFERROR(VLOOKUP(K197, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M197" s="12">
-        <v>46</v>
-      </c>
+      <c r="M197" s="12"/>
       <c r="N197" s="13"/>
       <c r="O197" s="13"/>
       <c r="P197" s="13"/>
@@ -12504,9 +12118,7 @@
         <f>IFERROR(VLOOKUP(K198, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M198" s="12">
-        <v>92</v>
-      </c>
+      <c r="M198" s="12"/>
       <c r="N198" s="13"/>
       <c r="O198" s="13"/>
       <c r="P198" s="13"/>
@@ -12539,9 +12151,7 @@
         <f>IFERROR(VLOOKUP(K199, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M199" s="12">
-        <v>92</v>
-      </c>
+      <c r="M199" s="12"/>
       <c r="N199" s="13"/>
       <c r="O199" s="13"/>
       <c r="P199" s="13"/>
@@ -12574,9 +12184,7 @@
         <f>IFERROR(VLOOKUP(K200, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M200" s="12">
-        <v>115</v>
-      </c>
+      <c r="M200" s="12"/>
       <c r="N200" s="13"/>
       <c r="O200" s="13"/>
       <c r="P200" s="13"/>
@@ -12609,9 +12217,7 @@
         <f>IFERROR(VLOOKUP(K201, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M201" s="12">
-        <v>230</v>
-      </c>
+      <c r="M201" s="12"/>
       <c r="N201" s="13"/>
       <c r="O201" s="13"/>
       <c r="P201" s="13"/>
@@ -12644,9 +12250,7 @@
         <f>IFERROR(VLOOKUP(K202, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.010</v>
       </c>
-      <c r="M202" s="12">
-        <v>69</v>
-      </c>
+      <c r="M202" s="12"/>
       <c r="N202" s="13"/>
       <c r="O202" s="13"/>
       <c r="P202" s="13"/>
